--- a/data/templates.xlsx
+++ b/data/templates.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="Templates"/>
@@ -1564,7 +1564,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1588,12 +1588,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1711,7 +1705,7 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
@@ -1741,22 +1735,22 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
@@ -1765,7 +1759,7 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
@@ -1777,16 +1771,16 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
@@ -2111,7 +2105,7 @@
     <col min="3" max="3" style="14" width="38.71928571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
@@ -2122,7 +2116,7 @@
         <v>488</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -2131,7 +2125,7 @@
       </c>
       <c r="C2" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -2140,7 +2134,7 @@
       </c>
       <c r="C3" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -2149,7 +2143,7 @@
       </c>
       <c r="C4" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -2158,7 +2152,7 @@
       </c>
       <c r="C5" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -2167,7 +2161,7 @@
       </c>
       <c r="C6" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -2176,7 +2170,7 @@
       </c>
       <c r="C7" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -2185,7 +2179,7 @@
       </c>
       <c r="C8" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -2194,7 +2188,7 @@
       </c>
       <c r="C9" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -2203,7 +2197,7 @@
       </c>
       <c r="C10" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -2212,7 +2206,7 @@
       </c>
       <c r="C11" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -14852,7 +14846,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="13" width="16.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="13" width="29.14785714285714" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="14" width="49.005" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="12" width="14.719285714285713" customWidth="1" bestFit="1"/>
   </cols>
@@ -14908,7 +14902,7 @@
         <v>69</v>
       </c>
       <c r="D4" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
@@ -14922,7 +14916,7 @@
         <v>69</v>
       </c>
       <c r="D5" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
@@ -14934,7 +14928,7 @@
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
@@ -14970,7 +14964,7 @@
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25">
@@ -14982,7 +14976,7 @@
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="4">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
@@ -14994,7 +14988,7 @@
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="4">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
@@ -15005,7 +14999,9 @@
         <v>77</v>
       </c>
       <c r="C12" s="20"/>
-      <c r="D12" s="7"/>
+      <c r="D12" s="7">
+        <v>41</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25">
       <c r="A13" s="4">
@@ -15031,7 +15027,9 @@
       <c r="C14" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="7"/>
+      <c r="D14" s="7">
+        <v>3</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25">
       <c r="A15" s="4">
@@ -15043,7 +15041,9 @@
       <c r="C15" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="7"/>
+      <c r="D15" s="7">
+        <v>23</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
       <c r="A16" s="4">
@@ -15055,7 +15055,9 @@
       <c r="C16" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="D16" s="7"/>
+      <c r="D16" s="7">
+        <v>8</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25">
       <c r="A17" s="4">
@@ -15065,7 +15067,9 @@
         <v>86</v>
       </c>
       <c r="C17" s="17"/>
-      <c r="D17" s="7"/>
+      <c r="D17" s="7">
+        <v>18</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="17.25">
       <c r="A18" s="4">
@@ -15075,7 +15079,9 @@
         <v>87</v>
       </c>
       <c r="C18" s="17"/>
-      <c r="D18" s="7"/>
+      <c r="D18" s="7">
+        <v>16</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="17.25">
       <c r="A19" s="4">
@@ -15085,7 +15091,9 @@
         <v>88</v>
       </c>
       <c r="C19" s="17"/>
-      <c r="D19" s="7"/>
+      <c r="D19" s="7">
+        <v>18</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25">
       <c r="A20" s="4">
@@ -15095,7 +15103,9 @@
         <v>89</v>
       </c>
       <c r="C20" s="17"/>
-      <c r="D20" s="7"/>
+      <c r="D20" s="7">
+        <v>41</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="17.25">
       <c r="A21" s="4">
@@ -15105,7 +15115,9 @@
         <v>90</v>
       </c>
       <c r="C21" s="17"/>
-      <c r="D21" s="7"/>
+      <c r="D21" s="7">
+        <v>41</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="17.25">
       <c r="A22" s="4">
@@ -15115,7 +15127,9 @@
         <v>91</v>
       </c>
       <c r="C22" s="17"/>
-      <c r="D22" s="7"/>
+      <c r="D22" s="7">
+        <v>13</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="17.25">
       <c r="A23" s="4">
@@ -15125,7 +15139,9 @@
         <v>92</v>
       </c>
       <c r="C23" s="17"/>
-      <c r="D23" s="7"/>
+      <c r="D23" s="7">
+        <v>9</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="17.25">
       <c r="A24" s="4">
@@ -15135,7 +15151,9 @@
         <v>93</v>
       </c>
       <c r="C24" s="17"/>
-      <c r="D24" s="7"/>
+      <c r="D24" s="7">
+        <v>34</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="17.25">
       <c r="A25" s="4">
@@ -15145,7 +15163,9 @@
         <v>94</v>
       </c>
       <c r="C25" s="17"/>
-      <c r="D25" s="7"/>
+      <c r="D25" s="7">
+        <v>34</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25">
       <c r="A26" s="4">
@@ -15155,7 +15175,9 @@
         <v>95</v>
       </c>
       <c r="C26" s="17"/>
-      <c r="D26" s="7"/>
+      <c r="D26" s="7">
+        <v>16</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="17.25">
       <c r="A27" s="4">
@@ -15165,7 +15187,9 @@
         <v>96</v>
       </c>
       <c r="C27" s="17"/>
-      <c r="D27" s="7"/>
+      <c r="D27" s="7">
+        <v>41</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="17.25">
       <c r="A28" s="4">
@@ -15175,7 +15199,9 @@
         <v>97</v>
       </c>
       <c r="C28" s="3"/>
-      <c r="D28" s="7"/>
+      <c r="D28" s="7">
+        <v>41</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="17.25">
       <c r="A29" s="4">
@@ -15185,7 +15211,9 @@
         <v>98</v>
       </c>
       <c r="C29" s="3"/>
-      <c r="D29" s="7"/>
+      <c r="D29" s="7">
+        <v>40</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="17.25">
       <c r="A30" s="4">
@@ -15195,7 +15223,9 @@
         <v>99</v>
       </c>
       <c r="C30" s="3"/>
-      <c r="D30" s="7"/>
+      <c r="D30" s="7">
+        <v>40</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25">
       <c r="A31" s="4">
@@ -15205,7 +15235,9 @@
         <v>100</v>
       </c>
       <c r="C31" s="3"/>
-      <c r="D31" s="7"/>
+      <c r="D31" s="7">
+        <v>21</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25">
       <c r="A32" s="4">
@@ -15215,7 +15247,9 @@
         <v>101</v>
       </c>
       <c r="C32" s="3"/>
-      <c r="D32" s="7"/>
+      <c r="D32" s="7">
+        <v>40</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="17.25">
       <c r="A33" s="4">
@@ -15225,7 +15259,9 @@
         <v>102</v>
       </c>
       <c r="C33" s="3"/>
-      <c r="D33" s="7"/>
+      <c r="D33" s="7">
+        <v>4</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="17.25">
       <c r="A34" s="4">
@@ -15235,7 +15271,9 @@
         <v>103</v>
       </c>
       <c r="C34" s="3"/>
-      <c r="D34" s="7"/>
+      <c r="D34" s="7">
+        <v>41</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
       <c r="A35" s="4">
@@ -15245,7 +15283,9 @@
         <v>104</v>
       </c>
       <c r="C35" s="3"/>
-      <c r="D35" s="7"/>
+      <c r="D35" s="7">
+        <v>41</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
       <c r="A36" s="4">
@@ -15255,7 +15295,9 @@
         <v>105</v>
       </c>
       <c r="C36" s="3"/>
-      <c r="D36" s="7"/>
+      <c r="D36" s="7">
+        <v>40</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
       <c r="A37" s="4">
@@ -15265,7 +15307,9 @@
         <v>106</v>
       </c>
       <c r="C37" s="3"/>
-      <c r="D37" s="7"/>
+      <c r="D37" s="7">
+        <v>8</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
       <c r="A38" s="4">
@@ -15275,7 +15319,9 @@
         <v>107</v>
       </c>
       <c r="C38" s="3"/>
-      <c r="D38" s="7"/>
+      <c r="D38" s="7">
+        <v>41</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
       <c r="A39" s="4">
@@ -15285,7 +15331,9 @@
         <v>108</v>
       </c>
       <c r="C39" s="3"/>
-      <c r="D39" s="7"/>
+      <c r="D39" s="7">
+        <v>41</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
       <c r="A40" s="4">
@@ -15295,7 +15343,9 @@
         <v>109</v>
       </c>
       <c r="C40" s="3"/>
-      <c r="D40" s="7"/>
+      <c r="D40" s="7">
+        <v>41</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
       <c r="A41" s="4">
@@ -15305,7 +15355,9 @@
         <v>110</v>
       </c>
       <c r="C41" s="3"/>
-      <c r="D41" s="7"/>
+      <c r="D41" s="7">
+        <v>22</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
       <c r="A42" s="4">
@@ -15315,7 +15367,9 @@
         <v>111</v>
       </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="7"/>
+      <c r="D42" s="7">
+        <v>34</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
       <c r="A43" s="4">
@@ -15325,7 +15379,9 @@
         <v>112</v>
       </c>
       <c r="C43" s="3"/>
-      <c r="D43" s="7"/>
+      <c r="D43" s="7">
+        <v>41</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
       <c r="A44" s="4">
@@ -15335,7 +15391,9 @@
         <v>113</v>
       </c>
       <c r="C44" s="3"/>
-      <c r="D44" s="7"/>
+      <c r="D44" s="7">
+        <v>34</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
       <c r="A45" s="4">
@@ -15345,7 +15403,9 @@
         <v>114</v>
       </c>
       <c r="C45" s="3"/>
-      <c r="D45" s="7"/>
+      <c r="D45" s="7">
+        <v>3</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
       <c r="A46" s="4">
@@ -15355,7 +15415,9 @@
         <v>115</v>
       </c>
       <c r="C46" s="3"/>
-      <c r="D46" s="7"/>
+      <c r="D46" s="7">
+        <v>3</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
       <c r="A47" s="4">
@@ -15365,7 +15427,9 @@
         <v>116</v>
       </c>
       <c r="C47" s="3"/>
-      <c r="D47" s="7"/>
+      <c r="D47" s="7">
+        <v>2</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
       <c r="A48" s="4">
@@ -15375,7 +15439,9 @@
         <v>117</v>
       </c>
       <c r="C48" s="3"/>
-      <c r="D48" s="7"/>
+      <c r="D48" s="7">
+        <v>40</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
       <c r="A49" s="4">
@@ -15387,7 +15453,9 @@
       <c r="C49" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="D49" s="7"/>
+      <c r="D49" s="7">
+        <v>22</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
       <c r="A50" s="4">
@@ -15399,7 +15467,9 @@
       <c r="C50" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="D50" s="7"/>
+      <c r="D50" s="7">
+        <v>22</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
       <c r="A51" s="4">
@@ -15409,7 +15479,9 @@
         <v>121</v>
       </c>
       <c r="C51" s="3"/>
-      <c r="D51" s="7"/>
+      <c r="D51" s="7">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/templates.xlsx
+++ b/data/templates.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="Templates"/>
@@ -1523,7 +1523,7 @@
     <t>prompt</t>
   </si>
   <si>
-    <t>topic / statement / terms</t>
+    <t>category</t>
   </si>
   <si>
     <t>I want to write an article about: "[TOPIC]". Give me references that support the hypothesis related to that topic.</t>
@@ -1532,7 +1532,7 @@
     <t>Explain the following statement: "[TOPIC]". Include references for each key claim.</t>
   </si>
   <si>
-    <t>Give me a 3-5 bullet summary of the following statement: "[TOPIC]". At the end of each bullet add references.</t>
+    <t>Give me a 3-5 bullet summary of [TOPIC], and at the end of each bullet add the reference.</t>
   </si>
   <si>
     <t>What is the current consensus on the statement "[TOPIC]"? Give me references.</t>
@@ -1544,10 +1544,10 @@
     <t>Write a short literature review on the statement "[TOPIC]". Include references.</t>
   </si>
   <si>
-    <t>Provide sources pro or against the statement "[TOPIC]".</t>
-  </si>
-  <si>
-    <t>Evaluate the strength of evidence across the state of the art on the statement "[TOPIC]". Compare.</t>
+    <t>Sources pro or against [TOPIC].</t>
+  </si>
+  <si>
+    <t>Evaluate the strength of evidence across the following studies on [TOPIC]. Compare:</t>
   </si>
   <si>
     <t>Evaluating the body of evidence on the statement "[TOPIC]". Summarize areas of agreement and disagreement and identify unresolved questions.</t>
@@ -1556,7 +1556,7 @@
     <t>I'm analyzing this article [LINK], what are other references related to the statement "[TOPIC]"?.</t>
   </si>
   <si>
-    <t>Give me a short definition of "[TERM]". Include references.</t>
+    <t>Define "[TERM]". Include references.</t>
   </si>
 </sst>
 </file>
@@ -2102,7 +2102,7 @@
   <cols>
     <col min="1" max="1" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="13" width="112.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="14" width="38.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="12" width="38.71928571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -2112,108 +2112,130 @@
       <c r="B1" s="37" t="s">
         <v>487</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="36" t="s">
         <v>488</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>489</v>
       </c>
-      <c r="C2" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="C2" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="C3" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="C3" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>491</v>
       </c>
-      <c r="C4" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="C4" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>492</v>
       </c>
-      <c r="C5" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="C5" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>493</v>
       </c>
-      <c r="C6" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="C6" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="C7" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>495</v>
       </c>
-      <c r="C8" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="C8" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="C9" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="C9" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>497</v>
       </c>
-      <c r="C10" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>498</v>
       </c>
-      <c r="C11" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="C11" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>499</v>
       </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="7">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15748,7 +15770,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -15762,7 +15784,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -15774,7 +15796,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -15788,7 +15810,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -15800,7 +15822,7 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -15812,7 +15834,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -15828,7 +15850,7 @@
       </c>
       <c r="F25" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -15840,7 +15862,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -15854,7 +15876,7 @@
       </c>
       <c r="F27" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -15868,7 +15890,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -15880,7 +15902,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -15892,7 +15914,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -15906,7 +15928,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -15918,7 +15940,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -15930,7 +15952,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -15944,7 +15966,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -15956,7 +15978,7 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -15970,7 +15992,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -15982,7 +16004,7 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -15996,7 +16018,7 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -16010,7 +16032,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -16022,7 +16044,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -16034,7 +16056,7 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -16046,7 +16068,7 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="7"/>
       <c r="B43" s="6"/>
       <c r="C43" s="3"/>

--- a/data/templates.xlsx
+++ b/data/templates.xlsx
@@ -2124,7 +2124,7 @@
         <v>489</v>
       </c>
       <c r="C2" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
@@ -2135,7 +2135,7 @@
         <v>490</v>
       </c>
       <c r="C3" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
@@ -2146,7 +2146,7 @@
         <v>491</v>
       </c>
       <c r="C4" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
@@ -2190,7 +2190,7 @@
         <v>495</v>
       </c>
       <c r="C8" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
@@ -2223,7 +2223,7 @@
         <v>498</v>
       </c>
       <c r="C11" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
@@ -2234,7 +2234,7 @@
         <v>499</v>
       </c>
       <c r="C12" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/templates.xlsx
+++ b/data/templates.xlsx
@@ -2124,7 +2124,7 @@
         <v>489</v>
       </c>
       <c r="C2" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
@@ -2135,7 +2135,7 @@
         <v>490</v>
       </c>
       <c r="C3" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
@@ -2146,7 +2146,7 @@
         <v>491</v>
       </c>
       <c r="C4" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
@@ -2168,7 +2168,7 @@
         <v>493</v>
       </c>
       <c r="C6" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
@@ -2179,7 +2179,7 @@
         <v>494</v>
       </c>
       <c r="C7" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
@@ -2190,7 +2190,7 @@
         <v>495</v>
       </c>
       <c r="C8" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
@@ -2201,7 +2201,7 @@
         <v>496</v>
       </c>
       <c r="C9" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
@@ -2212,7 +2212,7 @@
         <v>497</v>
       </c>
       <c r="C10" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
@@ -2223,7 +2223,7 @@
         <v>498</v>
       </c>
       <c r="C11" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
@@ -2234,7 +2234,7 @@
         <v>499</v>
       </c>
       <c r="C12" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
